--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-01-2026.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£14.55</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£18.15</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£24.97</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>£37.25</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationuk.co.uk', port=443): Max retries exceeded with url: /products/140mm-celotex-xr4140-pir-insulation-board-2400mm-x-1200mm-x-140mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£690.00</t>
+          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/celotex-xr4165-165mm-x-2-4m-x-1-2m-pallet-of-12 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>£890.00</t>
+          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/celotex-xr4200-200mm-x-2-4m-x-1-2m-pallet-of-12 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='www.planetinsulation.co.uk', port=443): Max retries exceeded with url: /products/celotex-cw4000-cavity-wall-boards?variant=42844829941997 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
